--- a/Samsung_final_H1_titles.xlsx
+++ b/Samsung_final_H1_titles.xlsx
@@ -8187,42 +8187,52 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
         <is>
           <t>BA61-04786B</t>
         </is>
       </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" s="2" t="n"/>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Bottom Base Cover (Graphite) - BA61-04786B</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Samsung Laptop Bottom Base Cover (Graphite) - BA61-04786B</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>57</v>
+      </c>
+      <c r="F172" t="inlineStr">
         <is>
           <t>ba61-04786b</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>Verified (page found)</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>https://samsungparts.com/products/ba61-04786b</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>Listing found but names no usable part type. Site title: Samsung BA61-04786B Null</t>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>High (exact part number confirmed)</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Name cleaned from exact-number listing. Site title: Samsung BA61-04786B Null</t>
         </is>
       </c>
     </row>
@@ -9115,42 +9125,52 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>AH81-15521A</t>
         </is>
       </c>
-      <c r="C193" s="2" t="n"/>
-      <c r="D193" s="2" t="n"/>
-      <c r="E193" s="2" t="n"/>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Main Assembly - AH81-15521A</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Main Assembly - AH81-15521A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
         <is>
           <t>ah81-15521a</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G193" s="3" t="inlineStr">
         <is>
           <t>Verified (page found)</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H193" s="3" t="inlineStr">
         <is>
           <t>https://samsungparts.com/products/ah81-15521a</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="J193" s="2" t="inlineStr">
-        <is>
-          <t>Listing found but names no usable part type. Page found but no usable name. Hint: title has no description; AH81 series audio/home theater part</t>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J193" s="3" t="inlineStr">
+        <is>
+          <t>Name cleaned from exact-number listing. Page found but no usable name. Hint: title has no description; AH81 series audio/home theater part</t>
         </is>
       </c>
     </row>
@@ -19828,42 +19848,52 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B431" s="2" t="inlineStr">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
         <is>
           <t>BN31-00022A</t>
         </is>
       </c>
-      <c r="C431" s="2" t="n"/>
-      <c r="D431" s="2" t="n"/>
-      <c r="E431" s="2" t="n"/>
-      <c r="F431" s="2" t="inlineStr">
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Samsung TV DC Fan - BN31-00022A</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Samsung TV DC Fan - BN31-00022A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>42</v>
+      </c>
+      <c r="F431" t="inlineStr">
         <is>
           <t>bn31-00022a</t>
         </is>
       </c>
-      <c r="G431" s="2" t="inlineStr">
+      <c r="G431" t="inlineStr">
         <is>
           <t>Verified (old-style page, handle not shown)</t>
         </is>
       </c>
-      <c r="H431" s="2" t="inlineStr">
+      <c r="H431" t="inlineStr">
         <is>
           <t>https://samsungparts.com/products/bn31-00022a</t>
         </is>
       </c>
-      <c r="I431" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="J431" s="2" t="inlineStr">
-        <is>
-          <t>Listing found but names no usable part type. Site title: BN31-00013A - FAN-CPU | Old-style PID-BN31-00022A link, but its title reads BN31-00013A - FAN-CPU (page says BN31-00013A is the new part for BN31-00022A); TV fan</t>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>High (exact part number confirmed)</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Name cleaned from exact-number listing. Site title: BN31-00013A - FAN-CPU | Old-style PID-BN31-00022A link, but its title reads BN31-00013A - FAN-CPU (page says BN31-00013A is the new part for BN31-00022A); TV fan</t>
         </is>
       </c>
     </row>
